--- a/Extracted_data_analysis/temperate/Output-Transformed_data/summary_split_counts_question_1_3.xlsx
+++ b/Extracted_data_analysis/temperate/Output-Transformed_data/summary_split_counts_question_1_3.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t xml:space="preserve">meso_substrate</t>
   </si>
@@ -156,9 +156,6 @@
     <t xml:space="preserve">func</t>
   </si>
   <si>
-    <t xml:space="preserve">sample</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trophic</t>
   </si>
   <si>
@@ -181,9 +178,6 @@
   </si>
   <si>
     <t xml:space="preserve">orientation</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Diversity</t>
   </si>
   <si>
     <t xml:space="preserve">disease</t>
@@ -588,7 +582,7 @@
         <v>42</v>
       </c>
       <c r="C2" t="n">
-        <v>8.3</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="3">
@@ -596,10 +590,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C3" t="n">
-        <v>52.96</v>
+        <v>52.85</v>
       </c>
     </row>
     <row r="4">
@@ -610,7 +604,7 @@
         <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>9.49</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="5">
@@ -618,10 +612,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C5" t="n">
-        <v>31.82</v>
+        <v>32.02</v>
       </c>
     </row>
     <row r="6">
@@ -632,7 +626,7 @@
         <v>12</v>
       </c>
       <c r="C6" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
     </row>
   </sheetData>
@@ -662,10 +656,10 @@
         <v>9</v>
       </c>
       <c r="B2" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C2" t="n">
-        <v>53.25</v>
+        <v>53.51</v>
       </c>
     </row>
     <row r="3">
@@ -676,7 +670,7 @@
         <v>189</v>
       </c>
       <c r="C3" t="n">
-        <v>35.06</v>
+        <v>34.87</v>
       </c>
     </row>
     <row r="4">
@@ -687,7 +681,7 @@
         <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>8.91</v>
+        <v>8.86</v>
       </c>
     </row>
   </sheetData>
@@ -720,7 +714,7 @@
         <v>51</v>
       </c>
       <c r="C2" t="n">
-        <v>9.46</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="3">
@@ -728,10 +722,10 @@
         <v>13</v>
       </c>
       <c r="B3" t="n">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C3" t="n">
-        <v>96.47</v>
+        <v>96.49</v>
       </c>
     </row>
     <row r="4">
@@ -742,7 +736,7 @@
         <v>67</v>
       </c>
       <c r="C4" t="n">
-        <v>12.43</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="5">
@@ -753,7 +747,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="6">
@@ -794,10 +788,10 @@
         <v>17</v>
       </c>
       <c r="B2" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C2" t="n">
-        <v>97.22</v>
+        <v>97.23</v>
       </c>
     </row>
     <row r="3">
@@ -808,7 +802,7 @@
         <v>33</v>
       </c>
       <c r="C3" t="n">
-        <v>6.12</v>
+        <v>6.09</v>
       </c>
     </row>
   </sheetData>
@@ -838,10 +832,10 @@
         <v>20</v>
       </c>
       <c r="B2" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C2" t="n">
-        <v>24.49</v>
+        <v>24.72</v>
       </c>
     </row>
     <row r="3">
@@ -852,7 +846,7 @@
         <v>258</v>
       </c>
       <c r="C3" t="n">
-        <v>47.87</v>
+        <v>47.6</v>
       </c>
     </row>
     <row r="4">
@@ -860,10 +854,10 @@
         <v>22</v>
       </c>
       <c r="B4" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C4" t="n">
-        <v>19.85</v>
+        <v>19.93</v>
       </c>
     </row>
     <row r="5">
@@ -874,7 +868,7 @@
         <v>95</v>
       </c>
       <c r="C5" t="n">
-        <v>17.63</v>
+        <v>17.53</v>
       </c>
     </row>
   </sheetData>
@@ -907,7 +901,7 @@
         <v>245</v>
       </c>
       <c r="C2" t="n">
-        <v>45.45</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="3">
@@ -915,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="B3" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C3" t="n">
-        <v>48.98</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="4">
@@ -929,7 +923,7 @@
         <v>118</v>
       </c>
       <c r="C4" t="n">
-        <v>21.89</v>
+        <v>21.77</v>
       </c>
     </row>
     <row r="5">
@@ -937,10 +931,10 @@
         <v>28</v>
       </c>
       <c r="B5" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>18.37</v>
+        <v>18.45</v>
       </c>
     </row>
     <row r="6">
@@ -948,10 +942,10 @@
         <v>29</v>
       </c>
       <c r="B6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" t="n">
-        <v>5.75</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="7">
@@ -962,7 +956,7 @@
         <v>40</v>
       </c>
       <c r="C7" t="n">
-        <v>7.42</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="8">
@@ -970,10 +964,10 @@
         <v>31</v>
       </c>
       <c r="B8" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C8" t="n">
-        <v>31.73</v>
+        <v>31.92</v>
       </c>
     </row>
     <row r="9">
@@ -984,7 +978,7 @@
         <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="10">
@@ -995,7 +989,7 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11">
@@ -1003,10 +997,10 @@
         <v>34</v>
       </c>
       <c r="B11" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C11" t="n">
-        <v>32.47</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="12">
@@ -1017,7 +1011,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>3.53</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="13">
@@ -1028,7 +1022,7 @@
         <v>62</v>
       </c>
       <c r="C13" t="n">
-        <v>11.5</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="14">
@@ -1039,7 +1033,7 @@
         <v>35</v>
       </c>
       <c r="C14" t="n">
-        <v>6.49</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="15">
@@ -1050,7 +1044,7 @@
         <v>149</v>
       </c>
       <c r="C15" t="n">
-        <v>27.64</v>
+        <v>27.49</v>
       </c>
     </row>
     <row r="16">
@@ -1061,7 +1055,7 @@
         <v>61</v>
       </c>
       <c r="C16" t="n">
-        <v>11.32</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="17">
@@ -1072,7 +1066,7 @@
         <v>50</v>
       </c>
       <c r="C17" t="n">
-        <v>9.28</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="18">
@@ -1083,7 +1077,7 @@
         <v>18</v>
       </c>
       <c r="C18" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="19">
@@ -1094,7 +1088,7 @@
         <v>13</v>
       </c>
       <c r="C19" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20">
@@ -1105,7 +1099,7 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="21">
@@ -1116,7 +1110,7 @@
         <v>10</v>
       </c>
       <c r="C21" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="22">
@@ -1124,10 +1118,10 @@
         <v>45</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>0.19</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="23">
@@ -1135,10 +1129,10 @@
         <v>46</v>
       </c>
       <c r="B23" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C23" t="n">
-        <v>4.45</v>
+        <v>7.75</v>
       </c>
     </row>
     <row r="24">
@@ -1146,10 +1140,10 @@
         <v>47</v>
       </c>
       <c r="B24" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C24" t="n">
-        <v>7.61</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="25">
@@ -1157,10 +1151,10 @@
         <v>48</v>
       </c>
       <c r="B25" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C25" t="n">
-        <v>3.53</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="26">
@@ -1168,10 +1162,10 @@
         <v>49</v>
       </c>
       <c r="B26" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>2.78</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="27">
@@ -1179,10 +1173,10 @@
         <v>50</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
-        <v>0.19</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="28">
@@ -1193,7 +1187,7 @@
         <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="29">
@@ -1201,10 +1195,10 @@
         <v>52</v>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.56</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="30">
@@ -1215,29 +1209,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>54</v>
-      </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>55</v>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>
@@ -1253,7 +1225,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1264,68 +1236,68 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B2" t="n">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C2" t="n">
-        <v>46.94</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B3" t="n">
         <v>30</v>
       </c>
       <c r="C3" t="n">
-        <v>5.57</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B4" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C4" t="n">
-        <v>51.95</v>
+        <v>51.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B5" t="n">
         <v>195</v>
       </c>
       <c r="C5" t="n">
-        <v>36.18</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B6" t="n">
         <v>68</v>
       </c>
       <c r="C6" t="n">
-        <v>12.62</v>
+        <v>12.55</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="8">
@@ -1336,7 +1308,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>
@@ -1352,7 +1324,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -1363,51 +1335,51 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B2" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C2" t="n">
-        <v>97.03</v>
+        <v>96.86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B3" t="n">
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B4" t="n">
         <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B5" t="n">
         <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B6" t="n">
         <v>2</v>
@@ -1418,18 +1390,18 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B8" t="n">
         <v>4</v>
@@ -1440,29 +1412,29 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B9" t="n">
         <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B11" t="n">
         <v>6</v>
